--- a/CE国試data/CE_questions_2020.xlsx
+++ b/CE国試data/CE_questions_2020.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
